--- a/calibration_ID2.xlsx
+++ b/calibration_ID2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="12">
   <si>
     <t>H</t>
   </si>
@@ -40,6 +40,15 @@
   </si>
   <si>
     <t>AirGrad</t>
+  </si>
+  <si>
+    <t>AirSTD</t>
+  </si>
+  <si>
+    <t>AirDelta</t>
+  </si>
+  <si>
+    <t>MeasLimitH</t>
   </si>
 </sst>
 </file>
@@ -218,6 +227,12 @@
       <c r="C8" s="0">
         <v>0</v>
       </c>
+      <c r="E8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="0">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
@@ -229,6 +244,12 @@
       <c r="C9" s="0">
         <v>0</v>
       </c>
+      <c r="E9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="0">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
@@ -240,6 +261,12 @@
       <c r="C10" s="0">
         <v>0</v>
       </c>
+      <c r="E10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="0">
+        <v>3130</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0">

--- a/calibration_ID2.xlsx
+++ b/calibration_ID2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="59" uniqueCount="13">
   <si>
     <t>H</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>MeasLimitH</t>
+  </si>
+  <si>
+    <t>WaveForm</t>
   </si>
 </sst>
 </file>
@@ -100,7 +103,7 @@
     <col min="1" max="1" width="5.140625" customWidth="true"/>
     <col min="2" max="2" width="6.140625" customWidth="true"/>
     <col min="3" max="3" width="5.42578125" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.5703125" customWidth="true"/>
     <col min="6" max="6" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -248,7 +251,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -278,6 +281,12 @@
       <c r="C11" s="0">
         <v>0</v>
       </c>
+      <c r="E11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
